--- a/resources/etsy/files/etsy-basics-take-home.xlsx
+++ b/resources/etsy/files/etsy-basics-take-home.xlsx
@@ -17,10 +17,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="£#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,11 +62,6 @@
       <color rgb="002F6F5E"/>
       <sz val="13"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -93,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -111,8 +106,6 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -478,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -499,7 +492,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -524,14 +516,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="7"/>
+        <v>4</v>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>ETSY'S FEES (yellow = check your own country)</t>
+          <t>ETSY'S FEES (US rates; check yours at etsy.com/legal/fees)</t>
         </is>
       </c>
     </row>
@@ -548,21 +539,21 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Payment processing — percent (UK 4%, US 3%)</t>
+          <t>Payment processing — percent (US 3%)</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Payment processing — fixed (UK £0.20, US $0.25)</t>
+          <t>Payment processing — fixed (US $0.25)</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12">
@@ -572,13 +563,13 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Regulatory operating fee (UK/EU only - your current rate)</t>
+          <t>Buyer's sales tax rate (0 if none) - processing is charged on it</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
@@ -595,7 +586,16 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="15"/>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Regulatory operating fee (outside the US only; US = 0)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Payment processing</t>
+          <t xml:space="preserve">  - Payment processing (on item + shipping + sales tax)</t>
         </is>
       </c>
       <c r="B18" s="7">
-        <f>-ROUND(B10*(B5+B6)+B11,2)</f>
+        <f>-ROUND(B10*(B5+B6)*(1+B13)+B11,2)</f>
         <v/>
       </c>
     </row>
@@ -643,11 +643,11 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Regulatory operating fee (if any)</t>
+          <t xml:space="preserve">  - Regulatory operating fee (outside the US only)</t>
         </is>
       </c>
       <c r="B20" s="7">
-        <f>-ROUND(B13*(B5+B6),2)</f>
+        <f>-ROUND(B15*(B5+B6),2)</f>
         <v/>
       </c>
     </row>
@@ -662,7 +662,6 @@
         <v/>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
@@ -685,7 +684,6 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
@@ -703,14 +701,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>A close estimate on current published rates, not a guaranteed exact amount:</t>
+          <t>A close estimate on current published rates, not a guaranteed exact amount. Sales tax</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>exchange rate, VAT on fees, and your country's regulatory fee can nudge it.</t>
+          <t>is not your money (Etsy collects and remits it); some states also tax Etsy's fees.</t>
         </is>
       </c>
     </row>
@@ -728,7 +726,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
@@ -742,10 +739,6 @@
           <t>ePORTS — your ecom source. eports.global.</t>
         </is>
       </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/etsy/files/etsy-basics-take-home.xlsx
+++ b/resources/etsy/files/etsy-basics-take-home.xlsx
@@ -736,7 +736,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
